--- a/data/trans_bre/P2C_R1-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,09</t>
+          <t>-0,26; 4,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,43</t>
+          <t>-2,86; 4,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,47</t>
+          <t>-1,33; 4,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 8,79</t>
+          <t>-11,79; 8,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-72,37; 286,09</t>
+          <t>-74,67; 262,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 661,53</t>
+          <t>-57,24; 716,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,27; 113,22</t>
+          <t>-59,36; 104,86</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 0,64</t>
+          <t>-6,02; 0,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,42</t>
+          <t>-1,66; 2,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,69</t>
+          <t>-1,93; 2,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 13,13</t>
+          <t>-6,46; 13,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,47; 193,92</t>
+          <t>-39,22; 183,67</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,39</t>
+          <t>-0,84; 3,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,51</t>
+          <t>-1,62; 1,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,3</t>
+          <t>-2,63; -0,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 28,23</t>
+          <t>0,03; 27,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 241,59</t>
+          <t>-1,81; 255,44</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,24</t>
+          <t>0,23; 3,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,96</t>
+          <t>0,38; 2,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,89</t>
+          <t>-0,91; 0,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,02; -7,24</t>
+          <t>-25,51; -7,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-50,43; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-95,31; -38,32</t>
+          <t>-94,6; -33,58</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,63</t>
+          <t>-1,09; 1,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,33</t>
+          <t>-1,19; 1,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 7,84</t>
+          <t>-9,77; 7,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,4; 66,28</t>
+          <t>-37,93; 63,85</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,42</t>
+          <t>0,14; 1,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,62</t>
+          <t>0,17; 1,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 18,08</t>
+          <t>-42,47; 18,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,8; 436,13</t>
+          <t>-70,81; 425,57</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,67</t>
+          <t>-0,32; 0,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,92</t>
+          <t>-0,23; 1,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,61</t>
+          <t>-0,55; 0,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 1,76</t>
+          <t>-12,99; 1,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 202,03</t>
+          <t>-43,81; 242,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 187,47</t>
+          <t>-20,6; 204,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-47,09; 97,05</t>
+          <t>-45,16; 109,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-65,47; 10,31</t>
+          <t>-65,12; 11,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R1-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9,38%</t>
+          <t>-2,0%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,68</t>
+          <t>-0,27; 4,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,48</t>
+          <t>-3,05; 4,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,72</t>
+          <t>-1,47; 4,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 8,73</t>
+          <t>-9,6; 9,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,67; 262,33</t>
+          <t>-71,75; 256,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,24; 716,44</t>
+          <t>-60,75; 718,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 104,86</t>
+          <t>-55,69; 177,11</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 0,53</t>
+          <t>-5,71; 0,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,49</t>
+          <t>-1,73; 2,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,8</t>
+          <t>-1,94; 2,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 13,09</t>
+          <t>-4,63; 13,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 183,67</t>
+          <t>-31,06; 228,35</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,3</t>
+          <t>15,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>107,62%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,78</t>
+          <t>-0,86; 3,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,59</t>
+          <t>-1,53; 1,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; -0,3</t>
+          <t>-2,89; -0,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 27,21</t>
+          <t>2,29; 29,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 255,44</t>
+          <t>8,25; 275,47</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-14,55</t>
+          <t>-6,58</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-77,53%</t>
+          <t>-37,98%</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,16</t>
+          <t>0,38; 3,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,83</t>
+          <t>0,28; 2,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,98</t>
+          <t>-0,95; 0,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,51; -7,09</t>
+          <t>-13,9; -0,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,43; —</t>
+          <t>-34,86; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,6; -33,58</t>
+          <t>-63,3; -1,81</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-2,58%</t>
+          <t>-1,61%</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,48</t>
+          <t>-1,26; 1,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,22</t>
+          <t>-1,24; 1,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 7,74</t>
+          <t>-9,61; 7,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,14 +1095,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 63,85</t>
+          <t>-40,28; 69,54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,5</t>
+          <t>0,17; 1,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,47; 18,76</t>
+          <t>-27,58; 18,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,81; 425,57</t>
+          <t>-60,36; 717,32</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,38</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-20,19%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,76</t>
+          <t>-0,36; 0,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,03</t>
+          <t>-0,2; 0,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,59</t>
+          <t>-0,6; 0,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 1,96</t>
+          <t>-2,56; 4,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 242,16</t>
+          <t>-43,69; 237,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 204,18</t>
+          <t>-22,99; 183,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 109,15</t>
+          <t>-47,87; 114,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-65,12; 11,02</t>
+          <t>-13,87; 36,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R1-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
